--- a/KAMCHATKA_BY_GROUP_KP.xlsx
+++ b/KAMCHATKA_BY_GROUP_KP.xlsx
@@ -818,12 +818,13 @@
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>+7 (351) 730-47-47 (пн-пт 8:30-17:30)</t>
+          <t>+7 (351) 730-47-47; +7 (922) 700-43-47
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>office@chsgs.ru; 166@ldtd.ru
+          <t>office@chsgs.ru
 chsgs.ru (лд.рф)</t>
         </is>
       </c>
@@ -858,7 +859,8 @@
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>+7 (495) 223-74-04</t>
+          <t>+7 (495) 223-74-04; 8-800-301-20-50
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -898,7 +900,8 @@
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>8-800-444-74-74; +7 900 093-04-01</t>
+          <t>8-800-444-74-74; +7 (351) 246-02-10; +7 (351) 245-02-10
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -938,7 +941,8 @@
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>+7 (749) 527-55-88 (как в каталоге productcenter — уточнить номер)</t>
+          <t>+7 (495) 275-58-88
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -978,7 +982,8 @@
       <c r="E8" s="4" t="n"/>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>+7 (495) 937-89-68</t>
+          <t>+7 (495) 937-89-68
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -1018,7 +1023,8 @@
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>через дилеров</t>
+          <t>через дилеров
+[только через дилеров (dn.ru)]</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -1058,7 +1064,8 @@
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>+7 (812) 458-55-97</t>
+          <t>+7 (812) 458-55-97
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -1098,7 +1105,8 @@
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>+7 (812) 611-03-77; 8-800-775-74-84</t>
+          <t>+7 (812) 611-03-77; 8-800-775-74-84
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -1138,12 +1146,13 @@
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>+7 (812) 325-90-51; +7 (495) 666-33-01</t>
+          <t>+7 (812) 325-90-51; +7 (495) 666-33-01
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>info@rosma.spb.ru (уточнить)
+          <t>info@rosma.spb.ru
 rosma.spb.ru</t>
         </is>
       </c>
@@ -7152,7 +7161,8 @@
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>8 800 350-91-13</t>
+          <t>8-800-350-91-13
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -7192,7 +7202,8 @@
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>8 800 444-00-28 (служба продаж); приёмная 8 800 222-15-44</t>
+          <t>8-800-444-00-28 (продажи); 8-800-222-15-44
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -7232,12 +7243,13 @@
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>+7 (495) 411-77-57 (Москва); Алексин +7 (48753) 2-70-25, 2-61-13 (по armtorg.ru)</t>
+          <t>+7 (495) 411-77-57
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>office@aztpa.ru; ngskr@aztpa.ru (клиновые задвижки)
+          <t>office@ogscomp.ru (указан на aztpa.ru)
 aztpa.ru</t>
         </is>
       </c>
@@ -7272,7 +7284,8 @@
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>+7 (34766) 2-99-10; отдел продаж (34766) 2-11-74, 2-13-57 (по ibprom.ru)</t>
+          <t>+7 (347) 662-99-10
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -7312,7 +7325,8 @@
       <c r="E8" s="4" t="n"/>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>+7 (812) 458-55-97; +7 (812) 334-92-39</t>
+          <t>+7 (812) 458-55-97; +7 (812) 334-92-39
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -7352,7 +7366,8 @@
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>+7 (495) 504-37-40; 8-800-777-95-16 (DN.ru)</t>
+          <t>+7 (495) 504-37-40; 8-800-777-95-16 (DN.ru)
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -7392,12 +7407,13 @@
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>уточнить на semlmz.ru</t>
+          <t>нет на сайте
+[semlmz.ru — контакты на сайте не опубликованы; не звонить, искать через дилеров]</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>уточнить на semlmz.ru
+          <t>нет на сайте
 semlmz.ru</t>
         </is>
       </c>
@@ -7432,7 +7448,8 @@
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>уточнить</t>
+          <t>уточнить
+[не найден — не использовать]</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -7472,7 +7489,8 @@
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>8 (495) 925-51-64</t>
+          <t>8 (495) 925-51-64
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -10111,7 +10129,8 @@
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>+7 (495) 792-57-57; 8-800-700-88-85</t>
+          <t>+7 (495) 792-57-57; 8-800-700-88-85
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -10151,7 +10170,8 @@
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>8-800-201-58-67; +7 (48142) 2-88-09, 2-83-67</t>
+          <t>8-800-201-58-67; +7 (48142) 2-88-09, 2-83-67
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -10191,7 +10211,8 @@
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>(49241) 2-32-41, 2-42-26</t>
+          <t>(49241) 2-32-41, 2-42-26
+[сайт armagus.ru не открылся 22.10 — номер из armtorg.ru, проверить звонком]</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -10231,12 +10252,13 @@
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>уточнить на сайте</t>
+          <t>8-800-700-77-85; +7 (495) 792-11-05
+[сайт teplo-sila.com, 22.10.2026]</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>уточнить на сайте
+          <t>marketing@teplo-sila.com
 teplo-sila.com (teplo-sila.by, teplo-sila.spb.ru)</t>
         </is>
       </c>
@@ -10271,7 +10293,8 @@
       <c r="E8" s="4" t="n"/>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>+7 (495) 504-37-40; 8-800-777-95-16 (DN.ru)</t>
+          <t>+7 (495) 504-37-40; 8-800-777-95-16 (DN.ru)
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -10311,7 +10334,8 @@
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>+7 (34766) 2-99-10</t>
+          <t>+7 (347) 662-99-10
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -10351,7 +10375,8 @@
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>+7 (812) 458-55-97</t>
+          <t>+7 (812) 458-55-97
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -10391,7 +10416,8 @@
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>+7 (495) 937-89-68; Хабаровск +7 (4212) 72-97-83</t>
+          <t>+7 (495) 937-89-68; Хабаровск +7 (4212) 72-97-83
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -10431,12 +10457,13 @@
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>+7 (991) 210-60-21</t>
+          <t>8-800-200-52-76; +7 (991) 210-60-21
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>reklama@pik-algrupp.ru (общий)
+          <t>sales@pik-algrupp.ru
 pik-algrupp.ru</t>
         </is>
       </c>
@@ -10471,7 +10498,8 @@
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>уточнить</t>
+          <t>уточнить
+[не найден — не использовать]</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
@@ -15647,7 +15675,8 @@
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>+7 (495) 937-89-68; Хабаровск +7 (4212) 72-97-83; Владивосток +7 (984) 159-21-64</t>
+          <t>+7 (495) 937-89-68; Хабаровск +7 (4212) 72-97-83; Владивосток +7 (984) 159-21-64
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -15687,7 +15716,8 @@
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>+7 (8412) 35-07-97; +7 (495) 668-10-92</t>
+          <t>+7 (495) 668-10-92; +7 (8412) 35-07-97; +7 (812) 309-54-81
+[сайт promarm.com, 22.10.2026]</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -15727,7 +15757,8 @@
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>(49241) 2-32-41, 2-42-26, 8-920-925-81-95 (отдел сбыта, по armtorg.ru)</t>
+          <t>(49241) 2-32-41, 2-42-26, 8-920-925-81-95 (отдел сбыта, по armtorg.ru)
+[сайт armagus.ru не открылся 22.10 — номер из armtorg.ru, проверить звонком]</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -15767,12 +15798,13 @@
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>+7 (351) 307-71-09</t>
+          <t>+7 (351) 307-71-09
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>info@zaoutk.ru
+          <t>info@aoutk.ru
 aoutk.ru</t>
         </is>
       </c>
@@ -16952,7 +16984,8 @@
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>+7 (4872) 72-47-16 (отдел реализации)</t>
+          <t>+7 (4872) 72-47-16 (отдел реализации)
+[сайт tulaprivod.ru не открылся 22.10 — проверить звонком]</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -16992,7 +17025,8 @@
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>(8352) 305-148, 305-221</t>
+          <t>+7 (8352) 30-51-48; 30-52-21; Москва +7 (495) 735-42-44
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -17032,7 +17066,8 @@
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>(49241) 2-32-41</t>
+          <t>(49241) 2-32-41
+[сайт armagus.ru не открылся 22.10 — номер из armtorg.ru, проверить звонком]</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -17072,7 +17107,8 @@
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>+7 (499) 653-65-06</t>
+          <t>+7 (499) 653-65-06
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -17112,7 +17148,8 @@
       <c r="E8" s="4" t="n"/>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>(8453) 75-48-28, 75-48-82</t>
+          <t>(8453) 75-48-28, 75-48-82
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -17152,7 +17189,8 @@
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>уточнить</t>
+          <t>уточнить
+[консультация, не поставщик]</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
